--- a/doc/sysml-xtext.xlsx
+++ b/doc/sysml-xtext.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yangr\Desktop\SysMLine\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Box\智能系统与计量工作组\_项目\【进行】SysMLine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817C03EB-99C2-4D00-93A9-543FF58CD99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A70E32-9374-4CD1-A59F-97406BE2DC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DefinitionElement" sheetId="1" r:id="rId1"/>
     <sheet name="UsageElement" sheetId="2" r:id="rId2"/>
     <sheet name="Expression" sheetId="4" r:id="rId3"/>
     <sheet name="Others" sheetId="3" r:id="rId4"/>
+    <sheet name="测试" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="316">
   <si>
     <t>Element</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1237,6 +1238,143 @@
   </si>
   <si>
     <t>?rendering</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RootNamespace</t>
+  </si>
+  <si>
+    <t>Instance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SysML::Namespace</t>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SysML::Namespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF0066CC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PackageBodyElement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>序号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>行号</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>名称</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>语句</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>映射完成度</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1247,7 +1385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1303,6 +1441,32 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0066CC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1339,7 +1503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1389,6 +1553,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1608,6 +1775,37 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1646,7 +1844,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1663,14 +1868,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1678,37 +1876,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1760,6 +1927,37 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1798,7 +1996,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
+          <bgColor rgb="FFF6DEF5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1812,7 +2017,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1823,44 +2028,6 @@
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF6DEF5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7233,14 +7400,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:N4 P1:XFD4 A2:XFD6 B7:AA7 AG7:XFD7 A8:XFD11 B12:AC13 AE12:XFD13 A14:XFD25 A26:N26 P26:XFD26 A27:XFD34 A35:N35 P35:XFD35 A36:XFD40 B41:AC42 AE41:XFD42 B43:XFD53 A54:XFD1048576">
-    <cfRule type="notContainsBlanks" dxfId="61" priority="81">
-      <formula>LEN(TRIM(A1))&gt;0</formula>
+    <cfRule type="endsWith" dxfId="61" priority="79" operator="endsWith" text="?">
+      <formula>RIGHT(A1,LEN("?"))="?"</formula>
     </cfRule>
     <cfRule type="endsWith" dxfId="60" priority="80" operator="endsWith" text=";|{}">
       <formula>RIGHT(A1,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="59" priority="79" operator="endsWith" text="?">
-      <formula>RIGHT(A1,LEN("?"))="?"</formula>
+    <cfRule type="notContainsBlanks" dxfId="59" priority="81">
+      <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:N4 P1:XFD4 A2:XFD6 B7:AA7 AG7:XFD7 A8:XFD11 B12:AC13 AE12:XFD13 A14:XFD25 A26:N26 P26:XFD26 B41:AC42 AE41:XFD42 B43:XFD53 A54:XFD1048576 A27:XFD34 A35:N35 P35:XFD35 A36:XFD40">
@@ -7249,34 +7416,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O4">
-    <cfRule type="endsWith" dxfId="56" priority="73" operator="endsWith" text="?">
+    <cfRule type="endsWith" dxfId="56" priority="72" operator="endsWith" text="*">
+      <formula>RIGHT(O1,LEN("*"))="*"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="55" priority="73" operator="endsWith" text="?">
       <formula>RIGHT(O1,LEN("?"))="?"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="55" priority="72" operator="endsWith" text="*">
-      <formula>RIGHT(O1,LEN("*"))="*"</formula>
+    <cfRule type="endsWith" dxfId="54" priority="74" operator="endsWith" text=";|{}">
+      <formula>RIGHT(O1,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="54" priority="75">
+    <cfRule type="notContainsBlanks" dxfId="53" priority="75">
       <formula>LEN(TRIM(O1))&gt;0</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="53" priority="74" operator="endsWith" text=";|{}">
-      <formula>RIGHT(O1,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O13">
-    <cfRule type="endsWith" dxfId="52" priority="51" operator="endsWith" text="*">
+    <cfRule type="endsWith" dxfId="52" priority="50" operator="endsWith" text="1">
+      <formula>RIGHT(O9,LEN("1"))="1"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="51" priority="51" operator="endsWith" text="*">
       <formula>RIGHT(O9,LEN("*"))="*"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="51" priority="52" operator="endsWith" text="?">
+    <cfRule type="endsWith" dxfId="50" priority="52" operator="endsWith" text="?">
       <formula>RIGHT(O9,LEN("?"))="?"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="50" priority="53" operator="endsWith" text=";|{}">
+    <cfRule type="endsWith" dxfId="49" priority="53" operator="endsWith" text=";|{}">
       <formula>RIGHT(O9,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="49" priority="54">
+    <cfRule type="notContainsBlanks" dxfId="48" priority="54">
       <formula>LEN(TRIM(O9))&gt;0</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="48" priority="50" operator="endsWith" text="1">
-      <formula>RIGHT(O9,LEN("1"))="1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O26">
@@ -7297,51 +7464,51 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O27:O34 Q35 O36:O58 A41:A53">
-    <cfRule type="notContainsBlanks" dxfId="41" priority="14">
-      <formula>LEN(TRIM(A27))&gt;0</formula>
+    <cfRule type="endsWith" dxfId="41" priority="10" operator="endsWith" text="1">
+      <formula>RIGHT(A27,LEN("1"))="1"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="40" priority="13" operator="endsWith" text=";|{}">
-      <formula>RIGHT(A27,LEN(";|{}"))=";|{}"</formula>
+    <cfRule type="endsWith" dxfId="40" priority="11" operator="endsWith" text="*">
+      <formula>RIGHT(A27,LEN("*"))="*"</formula>
     </cfRule>
     <cfRule type="endsWith" dxfId="39" priority="12" operator="endsWith" text="?">
       <formula>RIGHT(A27,LEN("?"))="?"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="38" priority="11" operator="endsWith" text="*">
-      <formula>RIGHT(A27,LEN("*"))="*"</formula>
+    <cfRule type="endsWith" dxfId="38" priority="13" operator="endsWith" text=";|{}">
+      <formula>RIGHT(A27,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="37" priority="10" operator="endsWith" text="1">
-      <formula>RIGHT(A27,LEN("1"))="1"</formula>
+    <cfRule type="notContainsBlanks" dxfId="37" priority="14">
+      <formula>LEN(TRIM(A27))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1">
-    <cfRule type="notContainsBlanks" dxfId="36" priority="9">
-      <formula>LEN(TRIM(Q1))&gt;0</formula>
+    <cfRule type="endsWith" dxfId="36" priority="6" operator="endsWith" text="*">
+      <formula>RIGHT(Q1,LEN("*"))="*"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="35" priority="8" operator="endsWith" text=";|{}">
+    <cfRule type="endsWith" dxfId="35" priority="7" operator="endsWith" text="?">
+      <formula>RIGHT(Q1,LEN("?"))="?"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="34" priority="8" operator="endsWith" text=";|{}">
       <formula>RIGHT(Q1,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="34" priority="7" operator="endsWith" text="?">
-      <formula>RIGHT(Q1,LEN("?"))="?"</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="33" priority="6" operator="endsWith" text="*">
-      <formula>RIGHT(Q1,LEN("*"))="*"</formula>
+    <cfRule type="notContainsBlanks" dxfId="33" priority="9">
+      <formula>LEN(TRIM(Q1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q18">
-    <cfRule type="endsWith" dxfId="32" priority="2" operator="endsWith" text="*">
+    <cfRule type="endsWith" dxfId="32" priority="1" operator="endsWith" text="1">
+      <formula>RIGHT(Q18,LEN("1"))="1"</formula>
+    </cfRule>
+    <cfRule type="endsWith" dxfId="31" priority="2" operator="endsWith" text="*">
       <formula>RIGHT(Q18,LEN("*"))="*"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="31" priority="3" operator="endsWith" text="?">
+    <cfRule type="endsWith" dxfId="30" priority="3" operator="endsWith" text="?">
       <formula>RIGHT(Q18,LEN("?"))="?"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="30" priority="4" operator="endsWith" text=";|{}">
+    <cfRule type="endsWith" dxfId="29" priority="4" operator="endsWith" text=";|{}">
       <formula>RIGHT(Q18,LEN(";|{}"))=";|{}"</formula>
     </cfRule>
-    <cfRule type="notContainsBlanks" dxfId="29" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="28" priority="5">
       <formula>LEN(TRIM(Q18))&gt;0</formula>
-    </cfRule>
-    <cfRule type="endsWith" dxfId="28" priority="1" operator="endsWith" text="1">
-      <formula>RIGHT(Q18,LEN("1"))="1"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8744,4 +8911,284 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDBC770-5FDC-4E86-A314-089F01CE1CA2}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9" style="19"/>
+    <col min="3" max="3" width="21.875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="19" customWidth="1"/>
+    <col min="5" max="5" width="24.25" style="19" customWidth="1"/>
+    <col min="6" max="6" width="37.125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="19" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19">
+        <v>38</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>